--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76.01304342059747</v>
+        <v>12.35211955584709</v>
       </c>
       <c r="D2" t="n">
-        <v>75.83054388278082</v>
+        <v>12.32246338095188</v>
       </c>
       <c r="E2" t="n">
-        <v>12.17905940088257</v>
+        <v>1.979097152643418</v>
       </c>
       <c r="F2" t="n">
-        <v>12.3065465439385</v>
+        <v>1.999813813390006</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.65492461883233</v>
+        <v>8.393925250560253</v>
       </c>
       <c r="D3" t="n">
-        <v>51.21745079490383</v>
+        <v>8.322835754171871</v>
       </c>
       <c r="E3" t="n">
-        <v>12.17905940088257</v>
+        <v>1.979097152643418</v>
       </c>
       <c r="F3" t="n">
-        <v>12.3065465439385</v>
+        <v>1.999813813390006</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
